--- a/data/trans_dic/DC-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/DC-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dolor crónico</t>
+          <t>Población con dolor crónico (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>13,47; 19,19</t>
+          <t>13,53; 18,91</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,01; 14,86</t>
+          <t>10,1; 15,12</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,66; 12,39</t>
+          <t>7,74; 12,22</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19,17; 25,46</t>
+          <t>19,0; 25,47</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>18,6; 24,59</t>
+          <t>18,88; 24,81</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,32; 29,47</t>
+          <t>22,67; 29,34</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,29; 22,02</t>
+          <t>16,26; 22,31</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>26,05; 38,92</t>
+          <t>27,8; 39,11</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>16,84; 21,1</t>
+          <t>16,98; 21,03</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16,82; 21,14</t>
+          <t>17,08; 21,34</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12,62; 16,56</t>
+          <t>12,43; 16,44</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>25,25; 31,49</t>
+          <t>25,95; 31,63</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>12,63; 17,12</t>
+          <t>12,33; 17,11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,46; 13,88</t>
+          <t>9,73; 13,72</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,38; 11,13</t>
+          <t>7,3; 10,8</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,6; 20,26</t>
+          <t>7,19; 20,04</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>23,39; 28,78</t>
+          <t>23,23; 28,96</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,61; 24,82</t>
+          <t>19,33; 25,05</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,05; 19,9</t>
+          <t>14,82; 19,8</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>36,21; 41,65</t>
+          <t>36,18; 41,45</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>18,38; 22,13</t>
+          <t>18,43; 22,14</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15,21; 18,75</t>
+          <t>15,18; 18,6</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11,75; 14,85</t>
+          <t>11,64; 14,73</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>17,24; 29,65</t>
+          <t>17,17; 29,75</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18,15; 24,35</t>
+          <t>18,32; 24,67</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,82; 10,24</t>
+          <t>5,91; 10,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,55; 10,67</t>
+          <t>6,56; 10,65</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>19,56; 26,48</t>
+          <t>19,72; 26,54</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>31,37; 38,55</t>
+          <t>31,42; 38,82</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20,33; 26,53</t>
+          <t>20,03; 26,55</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,05; 16,88</t>
+          <t>12,18; 17,12</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>38,11; 74,48</t>
+          <t>38,09; 75,65</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>25,95; 30,62</t>
+          <t>25,98; 30,72</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13,88; 17,86</t>
+          <t>13,76; 17,75</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9,73; 13,04</t>
+          <t>9,88; 13,16</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>30,57; 60,42</t>
+          <t>30,31; 58,87</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>16,58; 21,52</t>
+          <t>16,51; 21,27</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,74; 11,57</t>
+          <t>7,66; 11,67</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,75; 12,82</t>
+          <t>8,67; 12,82</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20,24; 25,97</t>
+          <t>20,41; 25,63</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>26,41; 32,02</t>
+          <t>26,45; 32,04</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,79; 27,47</t>
+          <t>21,99; 27,26</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,32; 24,8</t>
+          <t>19,17; 24,33</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>36,16; 53,25</t>
+          <t>36,15; 52,76</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>22,33; 26,16</t>
+          <t>22,25; 26,03</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>15,77; 19,18</t>
+          <t>15,74; 19,21</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14,75; 18,31</t>
+          <t>14,87; 18,33</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>29,75; 42,75</t>
+          <t>29,64; 40,88</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>16,32; 18,89</t>
+          <t>16,25; 18,88</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,4; 11,45</t>
+          <t>9,39; 11,5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,43; 10,62</t>
+          <t>8,48; 10,53</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16,15; 22,37</t>
+          <t>15,66; 22,37</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>26,44; 29,57</t>
+          <t>26,28; 29,45</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,43; 25,34</t>
+          <t>22,35; 25,28</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,94; 19,61</t>
+          <t>17,1; 19,89</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>37,77; 52,97</t>
+          <t>37,87; 52,64</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>21,7; 23,79</t>
+          <t>21,75; 23,72</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16,24; 18,14</t>
+          <t>16,34; 18,24</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13,14; 14,85</t>
+          <t>13,19; 14,88</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>28,45; 38,85</t>
+          <t>28,53; 37,95</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dolor crónico</t>
+          <t>Población con dolor crónico (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>93451; 133208</t>
+          <t>93923; 131263</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>70423; 104570</t>
+          <t>71047; 106352</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>51684; 83624</t>
+          <t>52215; 82462</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>121811; 161808</t>
+          <t>120750; 161833</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>128050; 169294</t>
+          <t>129971; 170748</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>155556; 205444</t>
+          <t>158047; 204494</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>109581; 148151</t>
+          <t>109390; 150129</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>188980; 282332</t>
+          <t>201629; 283654</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>232821; 291668</t>
+          <t>234691; 290708</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>235531; 296048</t>
+          <t>239240; 298921</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>170070; 223208</t>
+          <t>167525; 221491</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>343643; 428565</t>
+          <t>353178; 430478</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>121461; 164628</t>
+          <t>118587; 164538</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>96326; 141299</t>
+          <t>99044; 139655</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>75460; 113786</t>
+          <t>74681; 110373</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>102608; 241639</t>
+          <t>85811; 239086</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>226512; 278746</t>
+          <t>224919; 280452</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>202421; 256187</t>
+          <t>199480; 258581</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>156921; 207589</t>
+          <t>154581; 206471</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>347135; 399297</t>
+          <t>346859; 397321</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>354696; 427218</t>
+          <t>355764; 427430</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>311898; 384337</t>
+          <t>311284; 381404</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>242704; 306631</t>
+          <t>240447; 304311</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>370954; 637923</t>
+          <t>369348; 640125</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>123119; 165223</t>
+          <t>124276; 167374</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>44111; 77590</t>
+          <t>44789; 76644</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>49781; 81014</t>
+          <t>49857; 80883</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>137803; 186569</t>
+          <t>138997; 187019</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>214529; 263635</t>
+          <t>214877; 265463</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>157997; 206151</t>
+          <t>155660; 206378</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>94581; 132533</t>
+          <t>95600; 134382</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>355706; 695192</t>
+          <t>355512; 706130</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>353572; 417154</t>
+          <t>353967; 418544</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>213007; 274081</t>
+          <t>211196; 272382</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>150324; 201477</t>
+          <t>152640; 203188</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>500762; 989681</t>
+          <t>496490; 964261</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>156217; 202804</t>
+          <t>155528; 200369</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>73328; 109673</t>
+          <t>72604; 110602</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>82034; 120234</t>
+          <t>81286; 120164</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>187569; 240707</t>
+          <t>189169; 237556</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>274306; 332589</t>
+          <t>274763; 332772</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>229261; 288943</t>
+          <t>231285; 286697</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>201616; 258881</t>
+          <t>200060; 253998</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>395960; 583018</t>
+          <t>395797; 577721</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>442416; 518181</t>
+          <t>440730; 515648</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>315360; 383597</t>
+          <t>314817; 384066</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>292256; 362874</t>
+          <t>294589; 363217</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>601405; 864231</t>
+          <t>599337; 826559</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>534641; 619071</t>
+          <t>532336; 618642</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>322100; 392294</t>
+          <t>321648; 393929</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>286053; 360552</t>
+          <t>287743; 357414</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>558646; 774040</t>
+          <t>541691; 774077</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>893553; 999137</t>
+          <t>887963; 995197</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>798128; 901736</t>
+          <t>795179; 899494</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>600473; 694991</t>
+          <t>606242; 705030</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1402061; 1966429</t>
+          <t>1405779; 1954309</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1444561; 1583231</t>
+          <t>1447744; 1578929</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1134634; 1266868</t>
+          <t>1141083; 1274004</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>911753; 1030591</t>
+          <t>915013; 1032720</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2040610; 2786276</t>
+          <t>2046408; 2721471</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/DC-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/DC-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>37,92%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>30,12%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>13,53; 18,91</t>
+          <t>13,35; 19,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,1; 15,12</t>
+          <t>9,92; 15,37</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,74; 12,22</t>
+          <t>7,72; 12,03</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19,0; 25,47</t>
+          <t>18,65; 24,88</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>18,88; 24,81</t>
+          <t>18,65; 24,87</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,67; 29,34</t>
+          <t>22,38; 29,15</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,26; 22,31</t>
+          <t>15,92; 22,23</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>27,8; 39,11</t>
+          <t>35,25; 41,22</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>16,98; 21,03</t>
+          <t>16,75; 20,89</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17,08; 21,34</t>
+          <t>17,01; 21,18</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12,43; 16,44</t>
+          <t>12,79; 16,59</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>25,95; 31,63</t>
+          <t>27,98; 32,27</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>38,84%</t>
+          <t>38,92%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>29,1%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>12,33; 17,11</t>
+          <t>12,29; 16,97</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,73; 13,72</t>
+          <t>9,52; 13,81</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,3; 10,8</t>
+          <t>7,23; 10,88</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,19; 20,04</t>
+          <t>16,59; 21,9</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>23,23; 28,96</t>
+          <t>23,28; 28,91</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,33; 25,05</t>
+          <t>19,24; 24,81</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,82; 19,8</t>
+          <t>14,93; 20,02</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>36,18; 41,45</t>
+          <t>36,09; 41,52</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>18,43; 22,14</t>
+          <t>18,48; 22,34</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15,18; 18,6</t>
+          <t>15,35; 18,69</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11,64; 14,73</t>
+          <t>11,7; 14,8</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>17,17; 29,75</t>
+          <t>27,31; 31,05</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>52,83%</t>
+          <t>41,53%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>39,96%</t>
+          <t>32,37%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18,32; 24,67</t>
+          <t>18,51; 24,95</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,91; 10,12</t>
+          <t>5,83; 9,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,56; 10,65</t>
+          <t>6,51; 10,53</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>19,72; 26,54</t>
+          <t>19,96; 26,22</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>31,42; 38,82</t>
+          <t>31,24; 38,54</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20,03; 26,55</t>
+          <t>20,58; 26,77</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,18; 17,12</t>
+          <t>11,95; 17,36</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>38,09; 75,65</t>
+          <t>38,43; 44,78</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>25,98; 30,72</t>
+          <t>25,94; 30,71</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13,76; 17,75</t>
+          <t>13,91; 17,73</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9,88; 13,16</t>
+          <t>9,94; 13,3</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>30,31; 58,87</t>
+          <t>30,11; 34,78</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>41,17%</t>
+          <t>37,18%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>30,21%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>16,51; 21,27</t>
+          <t>16,36; 21,24</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,66; 11,67</t>
+          <t>7,89; 11,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,67; 12,82</t>
+          <t>8,87; 13,01</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20,41; 25,63</t>
+          <t>19,81; 25,13</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>26,45; 32,04</t>
+          <t>26,31; 31,87</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,99; 27,26</t>
+          <t>21,82; 26,96</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,17; 24,33</t>
+          <t>19,32; 24,64</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>36,15; 52,76</t>
+          <t>34,61; 39,7</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>22,25; 26,03</t>
+          <t>22,37; 26,09</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>15,74; 19,21</t>
+          <t>15,73; 19,14</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14,87; 18,33</t>
+          <t>14,84; 18,36</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>29,64; 40,88</t>
+          <t>28,44; 32,29</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>42,35%</t>
+          <t>38,77%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>30,35%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>16,25; 18,88</t>
+          <t>16,27; 19,01</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,39; 11,5</t>
+          <t>9,21; 11,44</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,48; 10,53</t>
+          <t>8,54; 10,6</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15,66; 22,37</t>
+          <t>20,0; 23,01</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>26,28; 29,45</t>
+          <t>26,41; 29,58</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,35; 25,28</t>
+          <t>22,37; 25,18</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,1; 19,89</t>
+          <t>17,06; 19,8</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>37,87; 52,64</t>
+          <t>37,36; 40,18</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>21,75; 23,72</t>
+          <t>21,63; 23,74</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16,34; 18,24</t>
+          <t>16,26; 18,17</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13,19; 14,88</t>
+          <t>13,27; 14,91</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>28,53; 37,95</t>
+          <t>29,32; 31,43</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>141352</t>
+          <t>150793</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>255886</t>
+          <t>278434</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>397239</t>
+          <t>429226</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>93923; 131263</t>
+          <t>92653; 132890</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>71047; 106352</t>
+          <t>69766; 108133</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>52215; 82462</t>
+          <t>52097; 81186</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>120750; 161833</t>
+          <t>128808; 171843</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>129971; 170748</t>
+          <t>128398; 171206</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>158047; 204494</t>
+          <t>155989; 203157</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>109390; 150129</t>
+          <t>107114; 149576</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>201629; 283654</t>
+          <t>258811; 302660</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>234691; 290708</t>
+          <t>231492; 288842</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>239240; 298921</t>
+          <t>238166; 296599</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>167525; 221491</t>
+          <t>172372; 223515</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>353178; 430478</t>
+          <t>398620; 459842</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>182735</t>
+          <t>200029</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>372361</t>
+          <t>417014</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>555097</t>
+          <t>617042</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>118587; 164538</t>
+          <t>118216; 163199</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>99044; 139655</t>
+          <t>96893; 140550</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>74681; 110373</t>
+          <t>73885; 111268</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>85811; 239086</t>
+          <t>174017; 229707</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>224919; 280452</t>
+          <t>225436; 279931</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>199480; 258581</t>
+          <t>198571; 256126</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>154581; 206471</t>
+          <t>155756; 208768</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>346859; 397321</t>
+          <t>386709; 444908</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>355764; 427430</t>
+          <t>356742; 431114</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>311284; 381404</t>
+          <t>314763; 383137</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>240447; 304311</t>
+          <t>241625; 305719</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>369348; 640125</t>
+          <t>579043; 658426</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>161505</t>
+          <t>185488</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>493128</t>
+          <t>337368</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>654633</t>
+          <t>522856</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>124276; 167374</t>
+          <t>125574; 169269</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>44789; 76644</t>
+          <t>44190; 74895</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>49857; 80883</t>
+          <t>49482; 79958</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>138997; 187019</t>
+          <t>160289; 210558</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>214877; 265463</t>
+          <t>213630; 263520</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>155660; 206378</t>
+          <t>159957; 208043</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>95600; 134382</t>
+          <t>93784; 136249</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>355512; 706130</t>
+          <t>312167; 363720</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>353967; 418544</t>
+          <t>353452; 418390</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>211196; 272382</t>
+          <t>213448; 272181</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>152640; 203188</t>
+          <t>153512; 205474</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>496490; 964261</t>
+          <t>486415; 561778</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>213097</t>
+          <t>221100</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>450798</t>
+          <t>416051</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>663895</t>
+          <t>637151</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>155528; 200369</t>
+          <t>154105; 200088</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>72604; 110602</t>
+          <t>74765; 111030</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>81286; 120164</t>
+          <t>83140; 121943</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>189169; 237556</t>
+          <t>196150; 248833</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>274763; 332772</t>
+          <t>273250; 331016</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>231285; 286697</t>
+          <t>229557; 283624</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>200060; 253998</t>
+          <t>201678; 257162</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>395797; 577721</t>
+          <t>387335; 444279</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>440730; 515648</t>
+          <t>443044; 516801</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>314817; 384066</t>
+          <t>314631; 382700</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>294589; 363217</t>
+          <t>294098; 363716</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>599337; 826559</t>
+          <t>599861; 680959</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>698690</t>
+          <t>757410</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1572173</t>
+          <t>1448866</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2270863</t>
+          <t>2206276</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>532336; 618642</t>
+          <t>533223; 622922</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>321648; 393929</t>
+          <t>315704; 391960</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>287743; 357414</t>
+          <t>289786; 359789</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>541691; 774077</t>
+          <t>706662; 812902</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>887963; 995197</t>
+          <t>892353; 999527</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>795179; 899494</t>
+          <t>795910; 895993</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>606242; 705030</t>
+          <t>604553; 701740</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1405779; 1954309</t>
+          <t>1396088; 1501379</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1447744; 1578929</t>
+          <t>1439946; 1579800</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1141083; 1274004</t>
+          <t>1135931; 1268886</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>915013; 1032720</t>
+          <t>920510; 1034593</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2046408; 2721471</t>
+          <t>2131668; 2284908</t>
         </is>
       </c>
     </row>
